--- a/data/trans_bre/P05B_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P05B_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-27,08%</t>
+          <t>-21,65%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,56</t>
+          <t>0,4; 3,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,94</t>
+          <t>-1,14; 0,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,59</t>
+          <t>0,02; 2,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,81</t>
+          <t>-1,95; 0,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 149,12</t>
+          <t>5,77; 150,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-58,19; 120,95</t>
+          <t>-57,39; 115,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 286,14</t>
+          <t>-5,63; 312,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-62,65; 62,63</t>
+          <t>-59,43; 57,29</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,95</t>
+          <t>0,24; 2,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,37</t>
+          <t>-0,46; 1,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,43</t>
+          <t>-0,22; 1,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,93</t>
+          <t>-0,1; 0,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 134,77</t>
+          <t>6,97; 122,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 115,46</t>
+          <t>-23,01; 101,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 145,11</t>
+          <t>-17,07; 149,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,63; 298,9</t>
+          <t>-18,61; 272,34</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-3,38%</t>
+          <t>-7,55%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,17</t>
+          <t>-1,01; 3,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,35</t>
+          <t>-3,14; 0,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,86</t>
+          <t>-1,27; 1,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,27</t>
+          <t>-1,63; 1,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 203,58</t>
+          <t>-26,08; 195,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-86,12; 49,84</t>
+          <t>-87,55; 53,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-67,09; 437,28</t>
+          <t>-65,02; 473,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-64,05; 125,2</t>
+          <t>-63,68; 106,4</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,67</t>
+          <t>0,81; 2,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,58</t>
+          <t>-0,66; 0,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,44</t>
+          <t>0,18; 1,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,71</t>
+          <t>-0,27; 0,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,44; 108,36</t>
+          <t>23,25; 101,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 42,91</t>
+          <t>-33,46; 44,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 134,4</t>
+          <t>9,59; 133,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 84,94</t>
+          <t>-20,95; 93,67</t>
         </is>
       </c>
     </row>
